--- a/MarketCaps.xlsx
+++ b/MarketCaps.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gerben\Google Drive\Financieel\IndexFondsen\KeuzeWelkIndexFonds\OnderzoekPerFonds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C55682-3805-400A-AF30-87C1088992BE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B56D6E-D69C-4FB5-9682-E056D52BE6AA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="29">
   <si>
     <t>MSCI ACWI IMI</t>
   </si>
@@ -191,7 +191,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -199,6 +199,8 @@
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -480,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:I68"/>
+  <dimension ref="B2:J75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.85546875" customWidth="1"/>
@@ -640,7 +642,7 @@
         <v>53092179.360330001</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>23</v>
       </c>
@@ -649,7 +651,7 @@
         <v>0.91676346456287972</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>8</v>
       </c>
@@ -657,7 +659,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>5</v>
       </c>
@@ -669,7 +671,7 @@
         <v>42386496.428819999</v>
       </c>
     </row>
-    <row r="21" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>6</v>
       </c>
@@ -681,7 +683,7 @@
         <v>5892804.9630000005</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>22</v>
       </c>
@@ -691,7 +693,7 @@
         <v>48279301.391819999</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>23</v>
       </c>
@@ -701,7 +703,7 @@
         <v>0.83365761481080891</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
         <v>8</v>
       </c>
@@ -709,7 +711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>12</v>
       </c>
@@ -721,7 +723,7 @@
         <v>29247582.4615</v>
       </c>
     </row>
-    <row r="27" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>13</v>
       </c>
@@ -733,7 +735,7 @@
         <v>4140889.9739999999</v>
       </c>
     </row>
-    <row r="28" spans="2:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>22</v>
       </c>
@@ -742,7 +744,7 @@
         <v>33388472.4355</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>23</v>
       </c>
@@ -751,7 +753,7 @@
         <v>0.57653183642527606</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="3" t="s">
         <v>8</v>
       </c>
@@ -759,7 +761,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>14</v>
       </c>
@@ -770,8 +772,12 @@
         <f>(100%-C32)*C5</f>
         <v>36311998.532969996</v>
       </c>
-    </row>
-    <row r="33" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E32" s="1">
+        <f>D32/D34</f>
+        <v>0.88467986570881629</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>15</v>
       </c>
@@ -782,8 +788,12 @@
         <f>(100%-C33)*C7</f>
         <v>4733355.7702799998</v>
       </c>
-    </row>
-    <row r="34" spans="2:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="E33" s="1">
+        <f>D33/D34</f>
+        <v>0.11532013429118358</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>22</v>
       </c>
@@ -792,7 +802,7 @@
         <v>41045354.30325</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>23</v>
       </c>
@@ -801,7 +811,7 @@
         <v>0.70874621589511044</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
         <v>8</v>
       </c>
@@ -809,7 +819,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>16</v>
       </c>
@@ -824,7 +834,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>17</v>
       </c>
@@ -837,7 +847,7 @@
         <v>5892804.9630000005</v>
       </c>
     </row>
-    <row r="40" spans="2:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>22</v>
       </c>
@@ -846,7 +856,7 @@
         <v>50889085.673</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>23</v>
       </c>
@@ -855,7 +865,7 @@
         <v>0.87872178260731904</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="3" t="s">
         <v>8</v>
       </c>
@@ -863,7 +873,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>16</v>
       </c>
@@ -877,8 +887,16 @@
       <c r="E44" s="6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="I44" s="1">
+        <f>D44/D47</f>
+        <v>0.8078042095533603</v>
+      </c>
+      <c r="J44" s="1">
+        <f>D44/E47</f>
+        <v>0.74355777050484018</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>17</v>
       </c>
@@ -890,8 +908,16 @@
         <f>(100%-C45)*C7</f>
         <v>5892804.9630000005</v>
       </c>
-    </row>
-    <row r="46" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I45" s="1">
+        <f>D45/D47</f>
+        <v>0.10579169167042771</v>
+      </c>
+      <c r="J45" s="1">
+        <f>D45/E47</f>
+        <v>9.7377846594648848E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>18</v>
       </c>
@@ -903,8 +929,20 @@
         <f>(100%-C46)*C6</f>
         <v>4812877.96851</v>
       </c>
-    </row>
-    <row r="47" spans="2:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="E46">
+        <f>D46*2</f>
+        <v>9625755.9370200001</v>
+      </c>
+      <c r="I46" s="1">
+        <f>D46/D47</f>
+        <v>8.640409877621201E-2</v>
+      </c>
+      <c r="J46" s="1">
+        <f>E46/E47</f>
+        <v>0.15906438290051106</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>22</v>
       </c>
@@ -913,8 +951,20 @@
         <f>SUM(D44:D46)</f>
         <v>55701963.641510002</v>
       </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E47">
+        <f>D44+D45+E46</f>
+        <v>60514841.610019997</v>
+      </c>
+      <c r="I47" s="7">
+        <f>SUM(I44:I46)</f>
+        <v>1</v>
+      </c>
+      <c r="J47" s="7">
+        <f>SUM(J44:J46)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>23</v>
       </c>
@@ -1037,7 +1087,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>27</v>
       </c>
@@ -1047,7 +1097,7 @@
         <v>44996280.710000001</v>
       </c>
     </row>
-    <row r="66" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>28</v>
       </c>
@@ -1057,7 +1107,7 @@
         <v>6370599.96</v>
       </c>
     </row>
-    <row r="67" spans="2:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>22</v>
       </c>
@@ -1066,13 +1116,110 @@
         <v>51366880.670000002</v>
       </c>
     </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>23</v>
       </c>
       <c r="D68" s="4">
         <f>D67/$C$3</f>
         <v>0.88697205603888618</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B70" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>14</v>
+      </c>
+      <c r="C71" s="2">
+        <v>0.193</v>
+      </c>
+      <c r="D71">
+        <f>(100%-C71)*C5</f>
+        <v>36311998.532969996</v>
+      </c>
+      <c r="E71" s="1">
+        <f>D71/D74</f>
+        <v>0.77435328662867275</v>
+      </c>
+      <c r="G71" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="H71" s="8">
+        <f>G71*E71</f>
+        <v>7.7435328662867281E-4</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" s="2">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="D72">
+        <f>(100%-C72)*C7</f>
+        <v>4733355.7702799998</v>
+      </c>
+      <c r="E72" s="1">
+        <f>D72/D74</f>
+        <v>0.10093880110099583</v>
+      </c>
+      <c r="G72" s="2">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="H72" s="8">
+        <f t="shared" ref="H72:H73" si="1">G72*E72</f>
+        <v>3.0281640330298749E-4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B73" t="s">
+        <v>26</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73">
+        <f>$C$6</f>
+        <v>5847968.3700000001</v>
+      </c>
+      <c r="E73" s="1">
+        <f>D73/D74</f>
+        <v>0.12470791227033134</v>
+      </c>
+      <c r="G73" s="2">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="H73" s="8">
+        <f t="shared" si="1"/>
+        <v>6.734227262597893E-4</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
+        <v>22</v>
+      </c>
+      <c r="D74" s="5">
+        <f>SUM(D71:D73)</f>
+        <v>46893322.673249997</v>
+      </c>
+      <c r="H74" s="2">
+        <f>SUM(H71:H73)</f>
+        <v>1.7505924161914494E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
+        <v>23</v>
+      </c>
+      <c r="D75" s="4">
+        <f>D74/C3</f>
+        <v>0.80972537719774818</v>
       </c>
     </row>
   </sheetData>
